--- a/data/trans_bre/IP08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 4,56</t>
+          <t>-9,01; 4,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 6,27</t>
+          <t>-7,62; 5,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,72</t>
+          <t>-7,16; 5,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 6,18</t>
+          <t>-7,43; 6,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 57,02</t>
+          <t>-60,95; 55,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 132,93</t>
+          <t>-68,58; 113,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-70,41; 115,05</t>
+          <t>-69,44; 116,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 87,48</t>
+          <t>-50,97; 84,48</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 6,56</t>
+          <t>-7,65; 6,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 6,97</t>
+          <t>-5,6; 7,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,3; -0,96</t>
+          <t>-10,16; -0,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 3,77</t>
+          <t>-11,14; 4,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 102,43</t>
+          <t>-59,5; 130,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 133,18</t>
+          <t>-49,96; 149,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-92,9; -0,34</t>
+          <t>-92,89; 15,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,83; 53,87</t>
+          <t>-68,37; 67,07</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,92; -0,96</t>
+          <t>-15,86; -1,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 3,22</t>
+          <t>-12,74; 3,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 4,5</t>
+          <t>-8,81; 4,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 1,06</t>
+          <t>-16,21; 0,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-86,21; -1,05</t>
+          <t>-86,14; -5,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 33,76</t>
+          <t>-68,98; 44,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 132,28</t>
+          <t>-82,7; 134,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-91,29; 36,5</t>
+          <t>-91,01; 30,53</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 3,54</t>
+          <t>-5,77; 3,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 5,65</t>
+          <t>-6,34; 5,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 6,0</t>
+          <t>-0,98; 6,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 6,01</t>
+          <t>-9,07; 6,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 49,97</t>
+          <t>-47,37; 55,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 43,95</t>
+          <t>-34,07; 40,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 166,89</t>
+          <t>-20,05; 181,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,18; 52,72</t>
+          <t>-55,52; 59,85</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 2,22</t>
+          <t>-10,49; 2,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 1,9</t>
+          <t>-12,27; 1,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 9,19</t>
+          <t>-2,58; 8,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 3,59</t>
+          <t>-24,36; 2,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-66,47; 28,5</t>
+          <t>-67,79; 26,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,5; 15,71</t>
+          <t>-58,48; 14,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 204,63</t>
+          <t>-28,09; 203,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-78,93; 42,35</t>
+          <t>-79,5; 30,87</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 3,76</t>
+          <t>-11,65; 3,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 9,18</t>
+          <t>-8,46; 8,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 2,38</t>
+          <t>-14,44; 0,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 5,51</t>
+          <t>-9,49; 4,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,85; 75,56</t>
+          <t>-76,35; 63,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,09; 170,57</t>
+          <t>-65,97; 152,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,86; 90,83</t>
+          <t>-91,1; 37,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,21; 184,1</t>
+          <t>-76,57; 148,78</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,83; -0,68</t>
+          <t>-5,8; -0,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 1,35</t>
+          <t>-4,77; 1,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,94</t>
+          <t>-2,64; 1,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 0,2</t>
+          <t>-7,73; 0,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,37; -6,64</t>
+          <t>-45,84; -7,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 11,25</t>
+          <t>-32,97; 8,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 33,57</t>
+          <t>-31,77; 31,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-48,93; 4,16</t>
+          <t>-47,74; 6,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 4,31</t>
+          <t>-9,74; 3,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 5,22</t>
+          <t>-7,59; 5,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 5,28</t>
+          <t>-6,87; 5,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 6,1</t>
+          <t>-6,7; 6,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-60,95; 55,74</t>
+          <t>-61,91; 52,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,58; 113,52</t>
+          <t>-63,11; 129,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-69,44; 116,8</t>
+          <t>-67,66; 134,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-50,97; 84,48</t>
+          <t>-53,57; 101,6</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 6,69</t>
+          <t>-8,19; 6,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 7,48</t>
+          <t>-6,01; 7,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -0,77</t>
+          <t>-10,17; -1,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 4,74</t>
+          <t>-11,32; 4,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,5; 130,28</t>
+          <t>-61,31; 103,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,96; 149,76</t>
+          <t>-53,16; 161,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-92,89; 15,85</t>
+          <t>-94,16; -14,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,37; 67,07</t>
+          <t>-67,83; 67,97</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -1,39</t>
+          <t>-15,31; -1,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 3,53</t>
+          <t>-12,53; 3,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 4,58</t>
+          <t>-8,85; 4,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 0,47</t>
+          <t>-15,42; 1,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-86,14; -5,72</t>
+          <t>-86,62; -0,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,98; 44,31</t>
+          <t>-69,19; 38,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-82,7; 134,98</t>
+          <t>-81,39; 135,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-91,01; 30,53</t>
+          <t>-90,66; 33,88</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 3,95</t>
+          <t>-5,45; 3,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 5,73</t>
+          <t>-6,78; 5,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 6,41</t>
+          <t>-1,24; 6,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 6,04</t>
+          <t>-9,08; 5,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,37; 55,49</t>
+          <t>-45,23; 45,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 40,83</t>
+          <t>-32,5; 37,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 181,96</t>
+          <t>-19,97; 198,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,52; 59,85</t>
+          <t>-54,61; 57,96</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 2,13</t>
+          <t>-10,06; 3,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 1,65</t>
+          <t>-11,71; 1,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 8,82</t>
+          <t>-2,25; 8,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 2,78</t>
+          <t>-25,8; 3,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-67,79; 26,34</t>
+          <t>-64,98; 43,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-58,48; 14,73</t>
+          <t>-58,02; 10,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 203,93</t>
+          <t>-26,5; 186,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-79,5; 30,87</t>
+          <t>-76,76; 43,32</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 3,52</t>
+          <t>-11,12; 4,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 8,78</t>
+          <t>-7,81; 9,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 0,55</t>
+          <t>-13,34; 1,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 4,93</t>
+          <t>-9,6; 4,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,35; 63,71</t>
+          <t>-76,39; 70,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 152,48</t>
+          <t>-66,13; 151,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-91,1; 37,15</t>
+          <t>-89,62; 64,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,57; 148,78</t>
+          <t>-80,28; 120,07</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -0,79</t>
+          <t>-5,78; -0,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 1,1</t>
+          <t>-4,65; 1,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,85</t>
+          <t>-2,59; 2,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 0,57</t>
+          <t>-8,17; 0,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-45,84; -7,23</t>
+          <t>-47,0; -6,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 8,98</t>
+          <t>-30,51; 10,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-31,77; 31,39</t>
+          <t>-31,22; 35,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 6,9</t>
+          <t>-51,11; 5,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,39%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 3,93</t>
+          <t>-9,32; 4,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 5,6</t>
+          <t>-7,63; 6,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 5,93</t>
+          <t>-7,1; 4,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 6,74</t>
+          <t>-6,74; 6,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-61,91; 52,47</t>
+          <t>-60,57; 57,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,11; 129,03</t>
+          <t>-63,8; 132,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,66; 134,88</t>
+          <t>-70,41; 115,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 101,6</t>
+          <t>-51,08; 93,64</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-26,36%</t>
+          <t>-26,11%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 6,32</t>
+          <t>-7,96; 6,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 7,87</t>
+          <t>-6,03; 6,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,17; -1,27</t>
+          <t>-10,3; -0,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 4,12</t>
+          <t>-11,18; 4,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 103,97</t>
+          <t>-60,77; 102,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,16; 161,6</t>
+          <t>-52,62; 133,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-94,16; -14,15</t>
+          <t>-92,9; -0,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,83; 67,97</t>
+          <t>-71,84; 57,47</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-7,19</t>
+          <t>-7,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-59,07%</t>
+          <t>-61,86%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -1,21</t>
+          <t>-15,92; -0,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 3,41</t>
+          <t>-12,62; 3,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 4,95</t>
+          <t>-8,4; 4,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 1,14</t>
+          <t>-16,07; 0,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-86,62; -0,94</t>
+          <t>-86,21; -1,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-69,19; 38,27</t>
+          <t>-68,65; 33,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-81,39; 135,2</t>
+          <t>-80,52; 132,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-90,66; 33,88</t>
+          <t>-91,28; 32,35</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,81</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-19,67%</t>
+          <t>-17,96%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 3,64</t>
+          <t>-5,88; 3,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 5,33</t>
+          <t>-6,06; 5,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 6,44</t>
+          <t>-1,55; 6,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 5,7</t>
+          <t>-7,49; 3,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 45,19</t>
+          <t>-49,0; 49,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,5; 37,42</t>
+          <t>-30,97; 43,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 198,58</t>
+          <t>-25,89; 166,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 57,96</t>
+          <t>-46,97; 33,51</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,59</t>
+          <t>-4,91</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-33,91%</t>
+          <t>-31,32%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 3,48</t>
+          <t>-10,7; 2,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 1,24</t>
+          <t>-12,19; 1,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 8,67</t>
+          <t>-2,03; 9,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 3,66</t>
+          <t>-20,84; 3,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 43,28</t>
+          <t>-66,47; 28,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 10,25</t>
+          <t>-59,5; 15,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 186,89</t>
+          <t>-23,98; 204,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-76,76; 43,32</t>
+          <t>-78,49; 42,65</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-1,86</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-24,24%</t>
+          <t>-22,73%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 4,15</t>
+          <t>-11,8; 3,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 9,34</t>
+          <t>-8,28; 9,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 1,89</t>
+          <t>-13,67; 2,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 4,64</t>
+          <t>-9,58; 6,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,39; 70,08</t>
+          <t>-76,85; 75,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,13; 151,95</t>
+          <t>-69,09; 170,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 64,64</t>
+          <t>-89,86; 90,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,28; 120,07</t>
+          <t>-75,74; 182,48</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,26</t>
+          <t>-3,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-25,2%</t>
+          <t>-24,53%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,78; -0,63</t>
+          <t>-5,83; -0,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,33</t>
+          <t>-4,81; 1,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,06</t>
+          <t>-2,57; 1,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 0,33</t>
+          <t>-7,1; -0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -6,15</t>
+          <t>-46,37; -6,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 10,23</t>
+          <t>-31,85; 11,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 35,18</t>
+          <t>-30,78; 33,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 5,06</t>
+          <t>-46,65; -0,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,38</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-20,25%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-9,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-14,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.382447992627755</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7860439881502673</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.057031409639132</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.01641933502141563</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2025337091065154</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.09414724952320581</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1401436948158305</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.001571588070415099</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,32; 4,56</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,63; 6,27</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,1; 4,72</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,74; 6,35</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-60,57; 57,02</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-63,8; 132,93</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-70,41; 115,05</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-51,08; 93,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.315750837662103</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.627706432095013</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.100969718885716</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.740247159214155</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.605703295147324</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.638031731554477</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.704058224380716</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.5107566190518039</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.556351154729408</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.269765861837712</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.716622633384768</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.351594690007786</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.570183535861771</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.329299213310432</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.150508148112782</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.9364154760444373</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-5,14</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-12,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-67,9%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-26,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,96; 6,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,03; 6,97</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-10,3; -0,96</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,18; 4,25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-60,77; 102,43</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-52,62; 133,18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-92,9; -0,34</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-71,84; 57,47</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.289181112204742</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5060056328992799</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-5.137821601615336</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-3.097051363840436</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1275760424016143</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.05896786833553793</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.679024085561077</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2611389092530284</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-8,26</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-4,48</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,24</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-7,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-59,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-32,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-29,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-61,86%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.96461213202421</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.031349111433555</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-10.2989140572977</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.18137003198122</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6077332806508229</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5261751756291035</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.9290338889371367</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7183864388227099</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-15,92; -0,96</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-12,62; 3,22</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,4; 4,5</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-16,07; 0,38</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-86,21; -1,05</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-68,65; 33,76</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-80,52; 132,28</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-91,28; 32,35</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.556938478390481</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.969145714377924</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-0.9596625963993547</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.252486946342617</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.024336694250634</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.331797015979574</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>-0.00339240806778111</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.5746626847659884</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,37</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-12,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-17,96%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-8.263236267270496</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.480316436107354</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.242788023371588</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-7.315342766486905</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5917235938591253</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3205415592318834</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.294490720820439</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.6186073716017918</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,88; 3,54</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,06; 5,65</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,55; 6,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,49; 3,6</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-49,0; 49,97</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-30,97; 43,95</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-25,89; 166,89</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-46,97; 33,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-15.92197705403991</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-12.62119317781421</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.404103968833535</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-16.07202812665</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.8620723972044229</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6864635617008309</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.8051899824457474</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.9127845514535272</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.960556407750434</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.217510374557317</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.501714702361555</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.377128489909515</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.01047963949003126</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3376200297345868</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.322792096612809</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.3234998082614181</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-4,31</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-5,1</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,14</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,91</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-33,9%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-30,45%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>45,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-31,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-10,7; 2,22</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-12,19; 1,9</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,03; 9,19</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-20,84; 3,93</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-66,47; 28,5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-59,5; 15,71</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-23,98; 204,63</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-78,49; 42,65</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.236522741976853</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.3257947747607626</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.368511854574174</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.47845926583289</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1247818061866806</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01904939683837118</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.4522507743501872</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1796444496163425</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-3,87</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-5,74</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,86</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-35,39%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-3,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-54,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-22,73%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.883800159680123</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.05903720124197</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.545798090273707</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-7.486618168572572</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4899796294285861</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3097129221633391</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2589268441124142</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4696990881853916</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-11,8; 3,76</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-8,28; 9,18</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-13,67; 2,38</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-9,58; 6,05</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-76,85; 75,56</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-69,09; 170,57</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-89,86; 90,83</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-75,74; 182,48</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.535628126254444</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.645852663827482</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.000557105197663</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.597885357359073</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4997367453636016</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.4394897599510906</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.668862272280505</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3351051294282825</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-1,78</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-27,63%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-13,08%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-4,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-24,53%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-4.309230141752114</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-5.097554061679493</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.137078813031831</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-4.909461073553437</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.3389800780096371</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.3044983912784542</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.4508601719014915</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.3132491093785298</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-5,83; -0,68</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,81; 1,35</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 1,94</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-7,1; -0,0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-46,37; -6,64</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-31,85; 11,25</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-30,78; 33,57</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-46,65; -0,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-10.70142713350023</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-12.18873431765475</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.032538976944473</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-20.83803214411832</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.6646906797337763</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.5949512287655202</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.239814849060842</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.7848698362859342</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.2245111607689</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.900750389548636</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.188597924753017</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.92797393234882</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2849779828241013</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1571132561065156</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.0462567952926</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.4264834077859008</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-3.873708877302566</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-0.3108860753203213</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-5.7424455851832</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.855835041074953</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3538816707300967</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.03284370564093776</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.5446959200761274</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.2272588884872505</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-11.80291519859739</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-8.279036692262565</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-13.66829859864581</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-9.576124394336185</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.7685262277801486</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6909352873161718</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.8985695444992493</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.7573585263468428</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3.760272061974649</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>9.180122891845109</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2.377700587592618</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>6.048922249025672</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.7556113904652286</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.705721687250434</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.9082852362808688</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>1.824778590814312</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-3.154199978747315</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-1.781351625529755</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.3448398382797646</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-3.095291835115058</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.2762636544263374</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.1308257011175373</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.04896876776017225</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.245318143721779</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-5.826214545840541</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.813044525795896</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.566258302094889</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-7.099057939635014</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.4637049078234264</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.3184581105169785</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.3078332695443835</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.4664759606925238</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-0.683895513815552</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.345792120323915</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.943386912703599</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-0.003984658655496977</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>-0.06635791270931193</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.1125440771334889</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.3357198813695794</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>-0.0006577637849471734</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
